--- a/daily_matches/job_matches_2026-05-13.xlsx
+++ b/daily_matches/job_matches_2026-05-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Backend ML Engineer</t>
+          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sterling Computers</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>North Sioux City, SD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, Pinecone, Prompt Engineering, PyTorch, MLflow, FastAPI</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0c294f11382975</t>
+          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Backend ML Engineer</t>
+          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sterling Computers</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, Pinecone, Prompt Engineering, PyTorch, MLflow, FastAPI</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8e8eb0ff879575</t>
+          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer, Machine Learning, Manufacturing Quality</t>
+          <t>Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Armor Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, Jenkins, Kafka, Hadoop</t>
+          <t>LangChain, RAG, LLaMA, Mistral, Pinecone, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae09bf0f698805e7</t>
+          <t>https://www.indeed.com/viewjob?jk=56657ac127da91fe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer, MLOps, Manufacturing Quality</t>
+          <t>Data Software Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Kafka, MySQL, MongoDB</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, Glue, Kinesis, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552f3d2b25f75144</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6014accfffb5fa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Software QA Engineer, Logistics</t>
+          <t>Full Stack Engineer - Laravel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>United States Postal Service</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB, NoSQL</t>
+          <t>RAG, Copilot, S3, Docker, Git, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3703a65a658398ce</t>
+          <t>https://www.indeed.com/viewjob?jk=6c136a581b5bd591</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Product Strategy Quant Analytics-Senior Associate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, FastAPI, Docker, Kubernetes, Git, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Snowflake, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,172 +671,172 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a4166ca835bce9</t>
+          <t>https://www.indeed.com/viewjob?jk=66de3efab695b30a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer, Full stack Machine Learning Platform, Manufacturing Quality</t>
+          <t>AI Data Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Kafka, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Databricks, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ea6be106b9be9b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7f0cb7dd1cecd1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Cloud Infrastructure Engineer (AI &amp; LLM Platforms)</t>
+          <t>Senior Machine Learning Engineer, Rider (Multiple Teams)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Q6 Cyber</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, Docker, Kubernetes, Terraform, Git, Kafka, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a3c6034334cd6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=48c7babb05456232</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Developer/Engineer</t>
+          <t>Senior Machine Learning Engineer, Rider (Multiple Teams)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sterling Computers</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26da044d5ac0597</t>
+          <t>https://www.indeed.com/viewjob?jk=022e67015a2ab83a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Developer/Engineer</t>
+          <t>Senior Machine Learning Engineer, Rider (Multiple Teams)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sterling Computers</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>North Sioux City, SD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667286ae4576a5d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c93294a1b10bdfb6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Data Scientist, AI Analytics</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Assurant</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Python, SQL</t>
+          <t>Data Scientist, Prompt Engineering, TensorFlow, PyTorch, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,462 +846,112 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=728da613cb18b07f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Advanced Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB, Cassandra, NoSQL, SQL</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7337f694f054c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a52f304172a1aeb4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full-Stack Geospatial Data Engineer</t>
+          <t>Technical Customer Support Engineer Tier 3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dclimate</t>
+          <t>UVEye</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, S3, FastAPI, Docker, CI/CD, Terraform, Git, Dask, Python</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, Jenkins, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87695ed720de3e69</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5bcba24e05d251</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (5+ years)</t>
+          <t>Data Science Product Senior Associate</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Git, Databricks, Python, SQL, R, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sr AI Engineer I</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, Docker, Kubernetes, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76590e39a6c5bede</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer/Senior Machine Learning Engineer - Infra</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Genentech</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, S3, EC2, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2347467f0507d411</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Rapideagle</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=009d41a1c754c1aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>X-Energy</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Rockville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Git, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=691560cc69f5c157</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AI Application Developer III</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Love’s Travel Stops</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AI Application Developer III -Houston, TX</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Love’s Travel Stops</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Sage Publication</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d540dd568981d67</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Mobile Software Engineer- Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51d3e48ccfb51fa6</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Sr. Database Administrator</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Meridian Cooperative Inc</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, EC2, PostgreSQL, MongoDB, NoSQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aad5be160ea34501</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4d53132c4b1789</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ef197a4b4e5660</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-13.xlsx
+++ b/daily_matches/job_matches_2026-05-13.xlsx
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, MongoDB, NoSQL, Python</t>
+          <t>Data Scientist, RAG, S3, Glue, BigQuery, Kinesis, Git, Databricks, BigQuery, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6324c917198667</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>Software Engineerâ€“ Full Stack</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, MongoDB, NoSQL, Python</t>
+          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd6f9018a657390</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer</t>
+          <t>Supervisor - Cyber Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Armor Health</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Mistral, Pinecone, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB</t>
+          <t>RAG, S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56657ac127da91fe</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b7c33de4d899ac</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Software Engineer III</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cirkle Studio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, Glue, Kinesis, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, BigQuery, FastAPI, Snowflake, BigQuery, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6014accfffb5fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ba99a22f41cc89a1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Laravel</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>United States Postal Service</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Git, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c136a581b5bd591</t>
+          <t>https://www.indeed.com/viewjob?jk=eff13e64bcd71e93</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Product Strategy Quant Analytics-Senior Associate</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Snowflake, Tableau, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,94 +671,94 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66de3efab695b30a</t>
+          <t>https://www.indeed.com/viewjob?jk=029163143b0a8709</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Data Engineer II</t>
+          <t>Senior Associate - Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Databricks, Python, R, Scala</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7f0cb7dd1cecd1</t>
+          <t>https://www.indeed.com/viewjob?jk=be5a7bd5b0f4a400</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Rider (Multiple Teams)</t>
+          <t>Senior Associate - Full Stack Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c7babb05456232</t>
+          <t>https://www.indeed.com/viewjob?jk=dda0ca1a9eaf976b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Rider (Multiple Teams)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Disney Parks, Experiences and Products</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Docker, Snowflake, Tableau, Python, SQL, R, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022e67015a2ab83a</t>
+          <t>https://www.indeed.com/viewjob?jk=37d974b6baf0d29c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Rider (Multiple Teams)</t>
+          <t>Senior Software Engineer, GoLang - DSX MaxQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,94 +811,94 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93294a1b10bdfb6</t>
+          <t>https://www.indeed.com/viewjob?jk=bc366fe07a5a50a7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Analytics</t>
+          <t>Platform Reliability Engineer – Data, Content &amp; Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Prompt Engineering, TensorFlow, PyTorch, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Terraform, PostgreSQL, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728da613cb18b07f</t>
+          <t>https://www.indeed.com/viewjob?jk=43204d9b47ac68cd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Advanced Analytics Data Scientist</t>
+          <t>Associate Data Analyst (Project Hire/Internal Assignment)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Disney Parks, Experiences and Products</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Docker, Kubernetes, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52f304172a1aeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=de88915eef1f920a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Technical Customer Support Engineer Tier 3</t>
+          <t>Senior Data Analyst (Project Hire/Internal Assignment)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UVEye</t>
+          <t>Disney Parks, Experiences and Products</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Jenkins, Git, Python, R, Scala</t>
+          <t>Data Scientist, Docker, Kubernetes, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5bcba24e05d251</t>
+          <t>https://www.indeed.com/viewjob?jk=655292bcc09ed104</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Science Product Senior Associate</t>
+          <t>Associate Data Analyst (Project Hire/Internal Assignment)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Python, SQL, R, Scala, A/B Testing</t>
+          <t>Data Scientist, Docker, Kubernetes, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ef197a4b4e5660</t>
+          <t>https://www.indeed.com/viewjob?jk=847f5f669919fcf1</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-13.xlsx
+++ b/daily_matches/job_matches_2026-05-13.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML (Machine Learning) Engineering Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, BigQuery, Kinesis, Git, Databricks, BigQuery, PySpark</t>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, TensorFlow, PyTorch, XGBoost, MLflow, Docker, Kubernetes, Apache Airflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6324c917198667</t>
+          <t>https://www.indeed.com/viewjob?jk=c5732db1baec0796</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineerâ€“ Full Stack</t>
+          <t>0000001423.AI ENGINEER II.INFO TECH - DATA AND AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Dallas County</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>AI Engineer, Data Scientist, RAG, Data Lake, Kinesis, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd6f9018a657390</t>
+          <t>https://www.indeed.com/viewjob?jk=8e292fecba5a3f54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Supervisor - Cyber Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>DELVIX EDGE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Generative AI, RAG, Data Lake, MLflow, CI/CD, Terraform, Git, Databricks, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b7c33de4d899ac</t>
+          <t>https://www.indeed.com/viewjob?jk=3059a32608f8fae5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Software Engineer - fullstack developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cirkle Studio</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, BigQuery, FastAPI, Snowflake, BigQuery, Python</t>
+          <t>RAG, Copilot, Redshift, Kinesis, Jenkins, Git, Redshift, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba99a22f41cc89a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d213cbff9fbff6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, MLOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff13e64bcd71e93</t>
+          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application Developer - ETL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>Copilot, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Tableau, MicroStrategy, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029163143b0a8709</t>
+          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Associate - Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -696,69 +696,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, R, Java</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5a7bd5b0f4a400</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Associate - Full Stack Developer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Terex Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, YOLO, S3, EC2, Git, Snowflake, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dda0ca1a9eaf976b</t>
+          <t>https://www.indeed.com/viewjob?jk=b44bc236dccc615e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Disney Parks, Experiences and Products</t>
+          <t>Trinity Health - IHA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Snowflake, Tableau, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>Gemini, Copilot, Git, MySQL, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37d974b6baf0d29c</t>
+          <t>https://www.indeed.com/viewjob?jk=427dad60a18585d2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, GoLang - DSX MaxQ</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Huntington Station, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Scala</t>
+          <t>CI/CD, Git, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc366fe07a5a50a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a0c4ecc4aa88ba</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer – Data, Content &amp; Analytics (Hybrid)</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>NBME</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, PostgreSQL, Tableau, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43204d9b47ac68cd</t>
+          <t>https://www.indeed.com/viewjob?jk=aee7f617d2ef571b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Data Analyst (Project Hire/Internal Assignment)</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Disney Parks, Experiences and Products</t>
+          <t>Infodat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, Kubernetes, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de88915eef1f920a</t>
+          <t>https://www.indeed.com/viewjob?jk=06e45a6e07950d80</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Analyst (Project Hire/Internal Assignment)</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Disney Parks, Experiences and Products</t>
+          <t>Vectra AI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, Kubernetes, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655292bcc09ed104</t>
+          <t>https://www.indeed.com/viewjob?jk=9ec49ceaea3954f7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate Data Analyst (Project Hire/Internal Assignment)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, Kubernetes, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Copilot, Synapse, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=847f5f669919fcf1</t>
+          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-13.xlsx
+++ b/daily_matches/job_matches_2026-05-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ML (Machine Learning) Engineering Consultant</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Wiss &amp; Company, LLP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, TensorFlow, PyTorch, XGBoost, MLflow, Docker, Kubernetes, Apache Airflow</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5732db1baec0796</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0eec70b87f9858</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0000001423.AI ENGINEER II.INFO TECH - DATA AND AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>Upwave</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Data Lake, Kinesis, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>RAG, Copilot, S3, Kinesis, Kubernetes, CI/CD, Terraform, Git, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e292fecba5a3f54</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8a2c5811cb8da3</t>
         </is>
       </c>
     </row>
@@ -543,20 +543,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DELVIX EDGE</t>
+          <t>Bridgeway Benefit Technologies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Maple Shade, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, MLflow, CI/CD, Terraform, Git, Databricks, PySpark, Tableau</t>
+          <t>RAG, Copilot, Kinesis, CI/CD, Terraform, Git, Databricks, Kafka, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3059a32608f8fae5</t>
+          <t>https://www.indeed.com/viewjob?jk=93da204448eced35</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer - fullstack developer</t>
+          <t>Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Paperless Post</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Redshift, Kinesis, Jenkins, Git, Redshift, MySQL, NoSQL, Python</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d213cbff9fbff6</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7244008409f34c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, MLOps</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Aegis Mobile</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Mobile, AL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Azure ML, Git, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
+          <t>https://www.indeed.com/viewjob?jk=3bd842a3f534f412</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Application Developer - ETL</t>
+          <t>Senior AI Engineer, Agentic Systems</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Copilot, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Tableau, MicroStrategy, SQL</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Cortex, BigQuery, Snowflake, Databricks, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
+          <t>https://www.indeed.com/viewjob?jk=638252e6bda90013</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer, Agentic Systems</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Git, Python, R</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Cortex, BigQuery, Snowflake, Databricks, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f0cbad0257d9fe9c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Terex Corporation</t>
+          <t>Pixability</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, YOLO, S3, EC2, Git, Snowflake, MySQL, SQL, R</t>
+          <t>RAG, Docker, CI/CD, Terraform, Snowflake, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44bc236dccc615e</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9f1061221d5d8c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Trinity Health - IHA</t>
+          <t>Industrial Electric Manufacturing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gemini, Copilot, Git, MySQL, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427dad60a18585d2</t>
+          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist - Innovation - PhD (Irving, TX)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Huntington Station, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CI/CD, Git, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, PyTorch, S3, EC2, MLflow, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a0c4ecc4aa88ba</t>
+          <t>https://www.indeed.com/viewjob?jk=88eaf917648d5ce8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NBME</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala</t>
+          <t>Copilot, CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee7f617d2ef571b</t>
+          <t>https://www.indeed.com/viewjob?jk=7084ba3880e82248</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Infodat</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Scala</t>
+          <t>Copilot, Synapse, Dataflow, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e45a6e07950d80</t>
+          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Page Wide Press Test Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vectra AI</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Corvallis, OR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec49ceaea3954f7</t>
+          <t>https://www.indeed.com/viewjob?jk=87099615f868a4de</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, People Innovation Labs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Copilot, Synapse, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Snowflake, Databricks, Hadoop, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,112 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
+          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer II</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>University of Wisconsin–Madison</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Madison, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2cc15ddc4debb2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>skyline career</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61b03a5025832ff3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Platform/MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bright Machines</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9a4bffdcd8152e0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-13.xlsx
+++ b/daily_matches/job_matches_2026-05-13.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Software Engineer, Sr. Consultant - Fullstack GenAI Enablement</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wiss &amp; Company, LLP</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Florham Park, NJ, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
+          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, S3, Kinesis, MLflow, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0eec70b87f9858</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c9240c1f60b916</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Upwave</t>
+          <t>9amHealth</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kinesis, Kubernetes, CI/CD, Terraform, Git, MySQL, NoSQL</t>
+          <t>RAG, Copilot, S3, Glue, Athena, Redshift, Docker, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8a2c5811cb8da3</t>
+          <t>https://www.indeed.com/viewjob?jk=204b0fbde6acaec8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bridgeway Benefit Technologies</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Maple Shade, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kinesis, CI/CD, Terraform, Git, Databricks, Kafka, Tableau, Power BI</t>
+          <t>RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Databricks, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93da204448eced35</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Paperless Post</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB</t>
+          <t>RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Databricks, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7244008409f34c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aegis Mobile</t>
+          <t>Premier Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mobile, AL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Azure ML, Git, Databricks, Tableau, Power BI, Python</t>
+          <t>RAG, BigQuery, Synapse, Git, Databricks, BigQuery, Kafka, Hadoop, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bd842a3f534f412</t>
+          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, Agentic Systems</t>
+          <t>AI COE Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Cortex, BigQuery, Snowflake, Databricks, BigQuery, Python, SQL</t>
+          <t>Data Scientist, LangChain, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638252e6bda90013</t>
+          <t>https://www.indeed.com/viewjob?jk=a48b9e31a7d1b56b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, Agentic Systems</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>9amHealth</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Cortex, BigQuery, Snowflake, Databricks, BigQuery, Python, SQL</t>
+          <t>RAG, Copilot, S3, Glue, Athena, Redshift, Data Lake, Git, Redshift, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0cbad0257d9fe9c</t>
+          <t>https://www.indeed.com/viewjob?jk=bea6d8d26e25a827</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pixability</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Terraform, Snowflake, MySQL, Python, SQL, R, Scala</t>
+          <t>RAG, Synapse, Data Lake, MLflow, CI/CD, Git, Databricks, PySpark, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9f1061221d5d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=25ad143bf215dca2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Industrial Electric Manufacturing</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Pinecone, Prompt Engineering, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
+          <t>https://www.indeed.com/viewjob?jk=852cb79f42a99c36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist - Innovation - PhD (Irving, TX)</t>
+          <t>Senior Automation Engineer(QA)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, PyTorch, S3, EC2, MLflow, Docker, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88eaf917648d5ce8</t>
+          <t>https://www.indeed.com/viewjob?jk=313e835ac21e71bb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Mimecast</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Glue, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7084ba3880e82248</t>
+          <t>https://www.indeed.com/viewjob?jk=e487d8e4722815c6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>SandStar Corp.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copilot, Synapse, Dataflow, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Docker, Kubernetes, PostgreSQL, MySQL, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
+          <t>https://www.indeed.com/viewjob?jk=c52348cdd52cd710</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Page Wide Press Test Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Corvallis, OR, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Docker, Terraform, Snowflake, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87099615f868a4de</t>
+          <t>https://www.indeed.com/viewjob?jk=24cdc5d33ce531fc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer, People Innovation Labs</t>
+          <t>Senior Machine Learning Engineer ( Automation Frameworks)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, S3, Snowflake, Databricks, Hadoop, Python, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
+          <t>https://www.indeed.com/viewjob?jk=a0ac105b89d1f93d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer II</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Whitehouse Station, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+          <t>AI Engineer, RAG, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2cc15ddc4debb2a</t>
+          <t>https://www.indeed.com/viewjob?jk=34039a1dfb3afd89</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Sr SW Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>skyline career</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, SQL, R</t>
+          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61b03a5025832ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=a941d4a6bca8f109</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Platform/MLOps Engineer</t>
+          <t>Senior Software Engineer, DL Libraries Infrastructure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bright Machines</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a4bffdcd8152e0</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a082a0c873f705</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-13.xlsx
+++ b/daily_matches/job_matches_2026-05-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer, Sr. Consultant - Fullstack GenAI Enablement</t>
+          <t>Data Scientist (Raleigh, NC - Hybrid)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, S3, Kinesis, MLflow, FastAPI, CI/CD</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, LightGBM, S3, Glue, Athena, Kinesis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c9240c1f60b916</t>
+          <t>https://www.indeed.com/viewjob?jk=93adc6e2c58559ea</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9amHealth</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Athena, Redshift, Docker, CI/CD, Terraform, Git</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=204b0fbde6acaec8</t>
+          <t>https://www.indeed.com/viewjob?jk=380cf25a1caed88b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Databricks, Kafka, MongoDB, NoSQL</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e9d4486acb8678</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Databricks, Kafka, MongoDB, NoSQL</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
+          <t>https://www.indeed.com/viewjob?jk=37bbb011f9ed9bce</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Premier Health</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Synapse, Git, Databricks, BigQuery, Kafka, Hadoop, NoSQL, Tableau</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
+          <t>https://www.indeed.com/viewjob?jk=cbab770adbb8a52e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI COE Analyst</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>23.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Databricks, Kafka</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a48b9e31a7d1b56b</t>
+          <t>https://www.indeed.com/viewjob?jk=a0eeb94a75d20a86</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9amHealth</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>21.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Athena, Redshift, Data Lake, Git, Redshift, MySQL</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, AWS SageMaker, Azure ML, EC2, Redshift</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bea6d8d26e25a827</t>
+          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid / Remote</t>
+          <t>Data Scientist / Software Engineer - REMOTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Binary Defense</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>21.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, MLflow, CI/CD, Git, Databricks, PySpark, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Azure ML, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ad143bf215dca2</t>
+          <t>https://www.indeed.com/viewjob?jk=decf8fd160fb3bfb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (contract)</t>
+          <t>Senior Software Engineer - Cloud Applications</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Pinecone, Prompt Engineering, Docker, Kubernetes, Git, Python</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=852cb79f42a99c36</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc7cb699ca48c49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer(QA)</t>
+          <t>Senior Software Engineer - Cloud Applications</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=313e835ac21e71bb</t>
+          <t>https://www.indeed.com/viewjob?jk=25dd86b5d7c3e977</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mimecast</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, SQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering, XGBoost</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e487d8e4722815c6</t>
+          <t>https://www.indeed.com/viewjob?jk=5f24ff146f8e0962</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Scientist, Professional Senior</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SandStar Corp.</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, PostgreSQL, MySQL, NoSQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, TensorFlow, NLTK, CI/CD, GitHub Actions, Git, Databricks, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52348cdd52cd710</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5365e2d852dbe0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Terraform, Snowflake, PostgreSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, S3, Glue, Athena, Data Lake, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cdc5d33ce531fc</t>
+          <t>https://www.indeed.com/viewjob?jk=3e724f2ee138a0dd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer ( Automation Frameworks)</t>
+          <t>V&amp;V Engineer – AI - Driven Testing &amp; Validation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0ac105b89d1f93d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e47c4f9f9521bc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Software Engineer, Backend Services</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Whitehouse Station, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>S3, Kinesis, FastAPI, Docker, GitHub Actions, Git, PySpark, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34039a1dfb3afd89</t>
+          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr SW Engineer</t>
+          <t>AI Native Engineer - Center for Advanced Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>RTI International</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, CI/CD, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,602 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a941d4a6bca8f109</t>
+          <t>https://www.indeed.com/viewjob?jk=deea1bdcc6b617b4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, DL Libraries Infrastructure</t>
+          <t>Senior Solutions Architect - HR Technology</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ConcertoCare</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, Pinecone, Prompt Engineering, CI/CD, Git, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8049c27b37d9064</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Databricks Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CMT Services INC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Adelphi, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BeyondTrust</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6715e4c4956d2eae</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cetera Financial Group</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>11.1</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a082a0c873f705</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Hugging Face, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a87d82f8e729c22</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Research Engineer, Asta</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>The Allen Institute for Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, spaCy, Docker, AKS, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f49a4e304daba07</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sr Java Engineer 202</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Git, PostgreSQL, MySQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=775b6d32c5b4a55a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Paramount Global US Inc</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Syracuse, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=741583eb645f2b61</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Agentic AI Developer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Calpion/Plutus Health</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b64fb0bdb4e6c4cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Solutions Engineer - Data Engineering</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SHI International</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, Databricks, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Backend / Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pinwheel</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1aab17836c12afbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Engineer II, IT Infrastructure</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cross River Bank</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Fort Lee, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, CI/CD, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b803a4954b4758f</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7226accc60cc22b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer- Early Career</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PR, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f7874101286c7ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Citian</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=860223c637760a32</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Git, MySQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76c6fb16ae455a71</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (Medical Spa Platform)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70380bf1ea04e252</t>
         </is>
       </c>
     </row>
